--- a/data/mogiten.xlsx
+++ b/data/mogiten.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2ad31227290ed1f/画像/ドキュメント/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suumi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{F95E626E-CD11-42BF-A949-169C784AE805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3984C0D-2CCB-4BF4-A741-D089CDD86693}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDC6BE52-4608-43CD-B4D1-F6FD0D4F3B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5D281CB1-87F8-464B-9D5C-E624D720B52A}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="247">
   <si>
-    <t>本場たこ焼き　MAIDO</t>
-  </si>
-  <si>
     <t>たこ焼き</t>
   </si>
   <si>
@@ -737,13 +734,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>物理学類1年</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>じゃぶじゃ部</t>
     <rPh sb="5" eb="6">
       <t>ブ</t>
@@ -909,6 +899,14 @@
     <rPh sb="5" eb="6">
       <t>カン</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>みつきんだよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テストだよおおおおおおおおおお</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1356,22 +1354,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -1379,19 +1377,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1399,19 +1397,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="115.5" x14ac:dyDescent="0.55000000000000004">
@@ -1419,19 +1417,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="148.5" x14ac:dyDescent="0.55000000000000004">
@@ -1439,19 +1437,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1459,19 +1457,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="247.5" x14ac:dyDescent="0.55000000000000004">
@@ -1479,19 +1477,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1499,19 +1497,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="313.5" x14ac:dyDescent="0.55000000000000004">
@@ -1519,19 +1517,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -1539,19 +1537,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1559,19 +1557,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1579,19 +1577,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1599,19 +1597,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1619,19 +1617,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="115.5" x14ac:dyDescent="0.55000000000000004">
@@ -1639,19 +1637,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="82.5" x14ac:dyDescent="0.55000000000000004">
@@ -1659,19 +1657,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="66" x14ac:dyDescent="0.55000000000000004">
@@ -1679,19 +1677,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1699,19 +1697,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -1719,19 +1717,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1739,19 +1737,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1759,19 +1757,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1779,19 +1777,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="148.5" x14ac:dyDescent="0.55000000000000004">
@@ -1799,19 +1797,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1819,19 +1817,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.55000000000000004">
@@ -1839,19 +1837,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -1859,19 +1857,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1879,19 +1877,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="99" x14ac:dyDescent="0.55000000000000004">
@@ -1899,19 +1897,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1919,19 +1917,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -1939,19 +1937,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1959,19 +1957,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="F31" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -1979,19 +1977,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F32" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="82.5" x14ac:dyDescent="0.55000000000000004">
@@ -1999,19 +1997,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="99" x14ac:dyDescent="0.55000000000000004">
@@ -2019,19 +2017,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2039,19 +2037,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="F35" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2059,19 +2057,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -2079,19 +2077,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F37" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2099,19 +2097,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2119,19 +2117,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="280.5" x14ac:dyDescent="0.55000000000000004">
@@ -2139,19 +2137,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F40" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2159,19 +2157,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2179,19 +2177,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="264" x14ac:dyDescent="0.55000000000000004">
@@ -2199,19 +2197,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2219,19 +2217,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="F44" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2239,19 +2237,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F45" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2259,19 +2257,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2279,19 +2277,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="231" x14ac:dyDescent="0.55000000000000004">
@@ -2299,19 +2297,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="82.5" x14ac:dyDescent="0.55000000000000004">
@@ -2319,19 +2317,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2339,19 +2337,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="F50" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2359,19 +2357,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -2379,19 +2377,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2399,19 +2397,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="181.5" x14ac:dyDescent="0.55000000000000004">
@@ -2419,19 +2417,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2439,19 +2437,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="115.5" x14ac:dyDescent="0.55000000000000004">
@@ -2459,19 +2457,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="198" x14ac:dyDescent="0.55000000000000004">
@@ -2479,19 +2477,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="148.5" x14ac:dyDescent="0.55000000000000004">
@@ -2499,19 +2497,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F58" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="247.5" x14ac:dyDescent="0.55000000000000004">
@@ -2519,19 +2517,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2539,19 +2537,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="214.5" x14ac:dyDescent="0.55000000000000004">
@@ -2559,19 +2557,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F61" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2579,19 +2577,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="165" x14ac:dyDescent="0.55000000000000004">
@@ -2599,19 +2597,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F63" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/mogiten.xlsx
+++ b/data/mogiten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365tsukuba-my.sharepoint.com/personal/s2411872_u_tsukuba_ac_jp/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{774EB184-0824-4ADE-8F15-4F8B03632B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{774EB184-0824-4ADE-8F15-4F8B03632B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10481B66-565E-408F-90F2-D8286B970844}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7E1DCC2F-C938-42F0-953B-40A56AF16552}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="236">
   <si>
     <t>テント番号</t>
     <rPh sb="3" eb="5">
@@ -104,13 +104,6 @@
   </si>
   <si>
     <t>チュロス</t>
-  </si>
-  <si>
-    <t>模擬店リスト</t>
-    <rPh sb="0" eb="3">
-      <t>モギテン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PR文</t>
@@ -1245,7 +1238,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1255,19 +1248,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1652,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76AF663-D031-4504-9A92-E16D8F3E1A8E}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1663,1285 +1647,1267 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>3</v>
+      <c r="B3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="C17" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>236</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>236</v>
+        <v>198</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1">
-        <v>23</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>230</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="6" t="s">
+      <c r="E27" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="C29" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="C31" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>5</v>
+        <v>205</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>235</v>
+        <v>211</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F38" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C40" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="F40" s="6" t="s">
+      <c r="C40" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="6" t="s">
+      <c r="C41" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>5</v>
+        <v>228</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1">
-        <v>41</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>235</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1">
-        <v>42</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>5</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1">
-        <v>43</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1">
-        <v>44</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>236</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1">
-        <v>45</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F48" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F50" s="6" t="s">
+      <c r="C50" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F51" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E54" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="D54" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1">
-        <v>53</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="F57" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1">
-        <v>55</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="6" t="s">
+      <c r="C59" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F60" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F61" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F62" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C63" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D63" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="1">
-        <v>61</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="1">
-        <v>62</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="6" t="s">
+      <c r="D63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+      <c r="E63" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -2953,23 +2919,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="03b0a243-51b5-406a-add1-2b6cc07b03cb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010082B22328A438ED4797BAD6B954B59B26" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2f675862f3a94272e87238a79eef03f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="03b0a243-51b5-406a-add1-2b6cc07b03cb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6328695d8b744b809b1858f2bdfc1890" ns3:_="">
     <xsd:import namespace="03b0a243-51b5-406a-add1-2b6cc07b03cb"/>
@@ -3119,6 +3068,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="03b0a243-51b5-406a-add1-2b6cc07b03cb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA73CC01-69B4-4587-BC3A-2572801A4800}">
   <ds:schemaRefs>
@@ -3128,30 +3094,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C27E8A5-5912-4B68-BDC5-92D802013F13}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03b0a243-51b5-406a-add1-2b6cc07b03cb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3D56688-1D99-4E39-B396-2EF8066E9500}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB56473B-12EB-4D47-B21C-BA215F9A7ED6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3167,4 +3109,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3D56688-1D99-4E39-B396-2EF8066E9500}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C27E8A5-5912-4B68-BDC5-92D802013F13}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03b0a243-51b5-406a-add1-2b6cc07b03cb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>